--- a/Capítulo04/RODIZIO-SP.xlsx
+++ b/Capítulo04/RODIZIO-SP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Publica\PROF RAUL\!!EXCEL FORMAÇÃO noite 18-03-25\PROF RAUL\Capítulo04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12495648-1132-4230-9B23-1DAAE2524286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{12495648-1132-4230-9B23-1DAAE2524286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{699D19B3-3171-4D83-BBF7-0F75CAA8BF1B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RODÍZIO" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>Rodízio</t>
   </si>
@@ -210,6 +210,27 @@
   </si>
   <si>
     <t>Katrina Feijó</t>
+  </si>
+  <si>
+    <t>FUNÇÕES</t>
+  </si>
+  <si>
+    <t>#=ESQUERDA(C5;3)</t>
+  </si>
+  <si>
+    <t>#=DIREITA(C5;4)</t>
+  </si>
+  <si>
+    <t>#=EXT.TEXTO(C5;2;2)</t>
+  </si>
+  <si>
+    <t>#=DIREITA(C5;1)</t>
+  </si>
+  <si>
+    <t>#=PROCV(G5;$K$7:$L$12;2)</t>
+  </si>
+  <si>
+    <t>#=SE(H5=$D$2;"Veículo no rodízio";"Livre para circular")</t>
   </si>
 </sst>
 </file>
@@ -219,7 +240,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,8 +293,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,6 +334,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99FFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -415,7 +502,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -431,93 +517,95 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="5">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color theme="7" tint="-0.499984740745262"/>
+        <color rgb="FF006100"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="3" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color theme="7" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="3" tint="-0.24994659260841701"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF99FFCC"/>
+      <color rgb="FFFF99CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -814,9 +902,86 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{5BF687A0-1F50-481F-975C-25A4A5B61DCC}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005502" version="1.0.0.13" store="WA200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;1XryDHJRqTEXgnMAW_BHL&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{77B46B6D-0301-4D39-A922-9EE026CB900C}">
+  <we:reference id="wa200005669" version="3.0.0.0" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005669" version="3.0.0.0" store="WA200005669" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension3.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A3A08BA8-490F-4F37-A464-3EB13BF30845}">
+  <we:reference id="wa200006230" version="1.0.0.0" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200006230" version="1.0.0.0" store="WA200006230" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -832,43 +997,46 @@
     <col min="11" max="11" width="14.140625" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" customWidth="1"/>
     <col min="14" max="14" width="8.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="51.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="22"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="17"/>
-      <c r="C2" s="17">
+      <c r="C2" s="24">
         <f ca="1">TODAY()</f>
-        <v>45763</v>
-      </c>
-      <c r="D2" s="18"/>
+        <v>46295</v>
+      </c>
+      <c r="D2" s="23" t="str">
+        <f ca="1">VLOOKUP(WEEKDAY(C2,2),K16:L22,2)</f>
+        <v>quarta-feira</v>
+      </c>
       <c r="E2" s="10"/>
       <c r="F2" s="11"/>
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="14"/>
@@ -879,7 +1047,7 @@
       <c r="H3" s="14"/>
       <c r="I3" s="15"/>
     </row>
-    <row r="4" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -907,8 +1075,11 @@
       <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O4" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
@@ -918,19 +1089,40 @@
       <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="3"/>
-      <c r="K5" s="19" t="s">
+      <c r="D5" s="26" t="str">
+        <f>LEFT(C5,3)</f>
+        <v>EME</v>
+      </c>
+      <c r="E5" s="27" t="str">
+        <f>RIGHT(C5,4)</f>
+        <v>1458</v>
+      </c>
+      <c r="F5" s="28" t="str">
+        <f>MID(C5,2,2)</f>
+        <v>ME</v>
+      </c>
+      <c r="G5" s="29" t="str">
+        <f>RIGHT(C5,1)</f>
+        <v>8</v>
+      </c>
+      <c r="H5" s="30" t="str">
+        <f>VLOOKUP(G5,$K$7:$L$12,2)</f>
+        <v>quinta-feira</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f ca="1">IF(H5=$D$2,"Veículo no rodízio","Livre para circular")</f>
+        <v>Livre para circular</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="20"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O5" s="31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>40</v>
       </c>
@@ -940,12 +1132,30 @@
       <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="3"/>
+      <c r="D6" s="16" t="str">
+        <f t="shared" ref="D6:D22" si="0">LEFT(C6,3)</f>
+        <v>EBA</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" ref="E6:E22" si="1">RIGHT(C6,4)</f>
+        <v>1105</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f t="shared" ref="F6:F22" si="2">MID(C6,2,2)</f>
+        <v>BA</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <f t="shared" ref="G6:G22" si="3">RIGHT(C6,1)</f>
+        <v>5</v>
+      </c>
+      <c r="H6" s="6" t="str">
+        <f t="shared" ref="H6:H22" si="4">VLOOKUP(G6,$K$7:$L$12,2)</f>
+        <v>quarta-feira</v>
+      </c>
+      <c r="I6" s="3" t="str">
+        <f t="shared" ref="I6:I22" ca="1" si="5">IF(H6=$D$2,"Veículo no rodízio","Livre para circular")</f>
+        <v>Veículo no rodízio</v>
+      </c>
       <c r="K6" s="5" t="s">
         <v>3</v>
       </c>
@@ -953,8 +1163,11 @@
         <v>1</v>
       </c>
       <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O6" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -964,12 +1177,30 @@
       <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="3"/>
+      <c r="D7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>EMC</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>5361</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>MC</v>
+      </c>
+      <c r="G7" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K7" s="6" t="str">
         <f>"0"</f>
         <v>0</v>
@@ -978,8 +1209,11 @@
         <v>5</v>
       </c>
       <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O7" s="33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
@@ -989,12 +1223,30 @@
       <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="3"/>
+      <c r="D8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>DRF</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>1787</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>RF</v>
+      </c>
+      <c r="G8" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H8" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K8" s="6" t="str">
         <f>"1"</f>
         <v>1</v>
@@ -1003,8 +1255,11 @@
         <v>6</v>
       </c>
       <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O8" s="34" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
@@ -1014,12 +1269,30 @@
       <c r="C9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="3"/>
+      <c r="D9" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>EJK</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>2350</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>JK</v>
+      </c>
+      <c r="G9" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K9" s="6" t="str">
         <f>"3"</f>
         <v>3</v>
@@ -1028,8 +1301,11 @@
         <v>7</v>
       </c>
       <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O9" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -1039,12 +1315,30 @@
       <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="3"/>
+      <c r="D10" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>DDI</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>7875</v>
+      </c>
+      <c r="F10" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>DI</v>
+      </c>
+      <c r="G10" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H10" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quarta-feira</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Veículo no rodízio</v>
+      </c>
       <c r="K10" s="6" t="str">
         <f>"5"</f>
         <v>5</v>
@@ -1053,8 +1347,11 @@
         <v>8</v>
       </c>
       <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O10" s="36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>46</v>
       </c>
@@ -1064,12 +1361,30 @@
       <c r="C11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="3"/>
+      <c r="D11" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>HYJ</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>3399</v>
+      </c>
+      <c r="F11" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>YJ</v>
+      </c>
+      <c r="G11" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="H11" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K11" s="6" t="str">
         <f>"7"</f>
         <v>7</v>
@@ -1079,7 +1394,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -1089,12 +1404,30 @@
       <c r="C12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="3"/>
+      <c r="D12" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>FRG</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>6766</v>
+      </c>
+      <c r="F12" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>RG</v>
+      </c>
+      <c r="G12" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="H12" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quarta-feira</v>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Veículo no rodízio</v>
+      </c>
       <c r="K12" s="6" t="str">
         <f>"9"</f>
         <v>9</v>
@@ -1104,7 +1437,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
@@ -1114,17 +1447,35 @@
       <c r="C13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="3"/>
+      <c r="D13" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>DER</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>1322</v>
+      </c>
+      <c r="F13" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>ER</v>
+      </c>
+      <c r="G13" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H13" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>segunda-feira</v>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>49</v>
       </c>
@@ -1134,18 +1485,36 @@
       <c r="C14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="3"/>
-      <c r="K14" s="19" t="s">
+      <c r="D14" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>EST</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>7653</v>
+      </c>
+      <c r="F14" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>ST</v>
+      </c>
+      <c r="G14" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="H14" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="I14" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
+      <c r="K14" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="L14" s="20"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L14" s="19"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>50</v>
       </c>
@@ -1155,12 +1524,30 @@
       <c r="C15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="3"/>
+      <c r="D15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>DRE</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>6798</v>
+      </c>
+      <c r="F15" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>RE</v>
+      </c>
+      <c r="G15" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="H15" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K15" s="5" t="s">
         <v>4</v>
       </c>
@@ -1168,7 +1555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>51</v>
       </c>
@@ -1178,12 +1565,30 @@
       <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="3"/>
+      <c r="D16" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>HIJ</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>7609</v>
+      </c>
+      <c r="F16" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>IJ</v>
+      </c>
+      <c r="G16" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="H16" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K16" s="6">
         <v>1</v>
       </c>
@@ -1201,12 +1606,30 @@
       <c r="C17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="3"/>
+      <c r="D17" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>DFR</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>8740</v>
+      </c>
+      <c r="F17" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>FR</v>
+      </c>
+      <c r="G17" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K17" s="6">
         <v>2</v>
       </c>
@@ -1224,12 +1647,30 @@
       <c r="C18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="3"/>
+      <c r="D18" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>EFT</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>4358</v>
+      </c>
+      <c r="F18" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>FT</v>
+      </c>
+      <c r="G18" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="H18" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="I18" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K18" s="6">
         <v>3</v>
       </c>
@@ -1247,12 +1688,30 @@
       <c r="C19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="3"/>
+      <c r="D19" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>ESX</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>1327</v>
+      </c>
+      <c r="F19" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>SX</v>
+      </c>
+      <c r="G19" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H19" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>quinta-feira</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K19" s="6">
         <v>4</v>
       </c>
@@ -1270,12 +1729,30 @@
       <c r="C20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="3"/>
+      <c r="D20" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>FRJ</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>7744</v>
+      </c>
+      <c r="F20" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>RJ</v>
+      </c>
+      <c r="G20" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="H20" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K20" s="6">
         <v>5</v>
       </c>
@@ -1293,12 +1770,30 @@
       <c r="C21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="3"/>
+      <c r="D21" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>HIK</v>
+      </c>
+      <c r="E21" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>5690</v>
+      </c>
+      <c r="F21" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>IK</v>
+      </c>
+      <c r="G21" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>sexta-feira</v>
+      </c>
+      <c r="I21" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K21" s="6">
         <v>6</v>
       </c>
@@ -1316,12 +1811,30 @@
       <c r="C22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="3"/>
+      <c r="D22" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>ESL</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>5533</v>
+      </c>
+      <c r="F22" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>SL</v>
+      </c>
+      <c r="G22" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="H22" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>terça-feira</v>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>Livre para circular</v>
+      </c>
       <c r="K22" s="6">
         <v>7</v>
       </c>
@@ -1335,6 +1848,14 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K5:L5"/>
   </mergeCells>
+  <conditionalFormatting sqref="I5:I22">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Veículo no rodízio"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Livre para circular"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -1377,12 +1898,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -1496,6 +2011,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7E47B2B-C01B-42F4-9E92-70A33E6F9662}">
   <ds:schemaRefs>
@@ -1505,14 +2026,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD930152-2F98-4D6D-A085-BFB4A081ABD2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8AACAE7-13DE-4D01-A2A5-F8C4FB9FAC1A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD930152-2F98-4D6D-A085-BFB4A081ABD2}"/>
 </file>